--- a/sharedata/excel/K-科技表(MagicTechData).xlsx
+++ b/sharedata/excel/K-科技表(MagicTechData).xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\策划文档\配置表\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ThroneOfAshes_Client\sharedata\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="133">
   <si>
     <t>科技表</t>
   </si>
@@ -146,6 +146,51 @@
     <t>size(need_tech_id)</t>
   </si>
   <si>
+    <t>临时金币产出</t>
+  </si>
+  <si>
+    <t>内政</t>
+  </si>
+  <si>
+    <t>$Lang$临时金币产出</t>
+  </si>
+  <si>
+    <t>科技图标_临时金币产出</t>
+  </si>
+  <si>
+    <t>$Lang$临时金币产出_说明</t>
+  </si>
+  <si>
+    <t>临时木材产出</t>
+  </si>
+  <si>
+    <t>$Lang$临时木材产出</t>
+  </si>
+  <si>
+    <t>科技图标_临时木材产出</t>
+  </si>
+  <si>
+    <t>$Lang$临时木材产出_说明</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>临时小兵攻击</t>
+  </si>
+  <si>
+    <t>战争</t>
+  </si>
+  <si>
+    <t>$Lang$临时小兵攻击</t>
+  </si>
+  <si>
+    <t>科技图标_临时小兵攻击</t>
+  </si>
+  <si>
+    <t>$Lang$临时小兵攻击_说明</t>
+  </si>
+  <si>
     <t>科技等级表</t>
   </si>
   <si>
@@ -191,6 +236,72 @@
     <t>size(need_item)</t>
   </si>
   <si>
+    <t>临时金币产出_1级</t>
+  </si>
+  <si>
+    <t>金币//木材</t>
+  </si>
+  <si>
+    <t>100//50</t>
+  </si>
+  <si>
+    <t>$Lang$临时金币产出_1级_说明</t>
+  </si>
+  <si>
+    <t>临时金币产出_2级</t>
+  </si>
+  <si>
+    <t>200//100</t>
+  </si>
+  <si>
+    <t>$Lang$临时金币产出_2级_说明</t>
+  </si>
+  <si>
+    <t>临时金币产出_3级</t>
+  </si>
+  <si>
+    <t>300//150</t>
+  </si>
+  <si>
+    <t>$Lang$临时金币产出_3级_说明</t>
+  </si>
+  <si>
+    <t>临时木材产出_1级</t>
+  </si>
+  <si>
+    <t>$Lang$临时木材产出_1级_说明</t>
+  </si>
+  <si>
+    <t>临时木材产出_2级</t>
+  </si>
+  <si>
+    <t>$Lang$临时木材产出_2级_说明</t>
+  </si>
+  <si>
+    <t>临时木材产出_3级</t>
+  </si>
+  <si>
+    <t>$Lang$临时木材产出_3级_说明</t>
+  </si>
+  <si>
+    <t>临时小兵攻击_1级</t>
+  </si>
+  <si>
+    <t>$Lang$临时小兵攻击_1级_说明</t>
+  </si>
+  <si>
+    <t>临时小兵攻击_2级</t>
+  </si>
+  <si>
+    <t>$Lang$临时小兵攻击_2级_说明</t>
+  </si>
+  <si>
+    <t>临时小兵攻击_3级</t>
+  </si>
+  <si>
+    <t>$Lang$临时小兵攻击_3级_说明</t>
+  </si>
+  <si>
     <t>科技分类表</t>
   </si>
   <si>
@@ -215,6 +326,18 @@
     <t>need_build_level</t>
   </si>
   <si>
+    <t>$Lang$科技分类_内政</t>
+  </si>
+  <si>
+    <t>科技图标_内政</t>
+  </si>
+  <si>
+    <t>$Lang$科技分类_战争</t>
+  </si>
+  <si>
+    <t>科技图标_战争</t>
+  </si>
+  <si>
     <t>战斗科技效果表</t>
   </si>
   <si>
@@ -257,6 +380,21 @@
     <t>ref(FightAttrData)</t>
   </si>
   <si>
+    <t>临时小兵攻击_1级_效果</t>
+  </si>
+  <si>
+    <t>小兵</t>
+  </si>
+  <si>
+    <t>攻击</t>
+  </si>
+  <si>
+    <t>临时小兵攻击_2级_效果</t>
+  </si>
+  <si>
+    <t>临时小兵攻击_3级_效果</t>
+  </si>
+  <si>
     <t>资源产出科技效果表</t>
   </si>
   <si>
@@ -273,6 +411,30 @@
   </si>
   <si>
     <t>output_bonus_rate</t>
+  </si>
+  <si>
+    <t>临时金币产出_1级_效果</t>
+  </si>
+  <si>
+    <t>金币</t>
+  </si>
+  <si>
+    <t>临时金币产出_2级_效果</t>
+  </si>
+  <si>
+    <t>临时金币产出_3级_效果</t>
+  </si>
+  <si>
+    <t>临时木材产出_1级_效果</t>
+  </si>
+  <si>
+    <t>木材</t>
+  </si>
+  <si>
+    <t>临时木材产出_2级_效果</t>
+  </si>
+  <si>
+    <t>临时木材产出_3级_效果</t>
   </si>
 </sst>
 </file>
@@ -301,6 +463,13 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -455,13 +624,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-      <b/>
-      <color rgb="FFFF0000"/>
-    </font>
   </fonts>
   <fills count="34">
     <fill>
@@ -789,148 +951,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -954,10 +1116,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1432,7 +1594,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:K9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelRow="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="14.2222222222222" style="2" customWidth="1"/>
     <col min="2" max="2" width="6.44444444444444" style="2" customWidth="1"/>
@@ -1612,87 +1774,87 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" ht="66.0" customHeight="1">
-      <c r="B7" t="n" s="6">
+    <row r="7" ht="66" customHeight="1" spans="1:11">
+      <c r="B7" s="6">
         <v>1</v>
       </c>
-      <c r="C7" t="str" s="7">
-        <v>临时金币产出</v>
-      </c>
-      <c r="D7" t="str" s="6">
-        <v>内政</v>
-      </c>
-      <c r="E7" t="str" s="7">
-        <v>$Lang$临时金币产出</v>
-      </c>
-      <c r="F7" t="str" s="7">
-        <v>科技图标_临时金币产出</v>
-      </c>
-      <c r="G7" t="str" s="7">
-        <v>$Lang$临时金币产出_说明</v>
-      </c>
-      <c r="H7" t="n" s="6">
+      <c r="C7" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="H7" s="6">
         <v>1</v>
       </c>
-      <c r="I7" t="n" s="6">
+      <c r="I7" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="8" ht="66.0" customHeight="1">
-      <c r="B8" t="n" s="6">
+    <row r="8" ht="66" customHeight="1" spans="1:11">
+      <c r="B8" s="6">
         <v>2</v>
       </c>
-      <c r="C8" t="str" s="7">
-        <v>临时木材产出</v>
-      </c>
-      <c r="D8" t="str" s="6">
-        <v>内政</v>
-      </c>
-      <c r="E8" t="str" s="7">
-        <v>$Lang$临时木材产出</v>
-      </c>
-      <c r="F8" t="str" s="7">
-        <v>科技图标_临时木材产出</v>
-      </c>
-      <c r="G8" t="str" s="7">
-        <v>$Lang$临时木材产出_说明</v>
-      </c>
-      <c r="H8" t="n" s="6">
+      <c r="C8" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="H8" s="6">
         <v>2</v>
       </c>
-      <c r="I8" t="n" s="6">
+      <c r="I8" s="6">
         <v>1</v>
       </c>
-      <c r="J8" t="str" s="6">
-        <v>临时金币产出</v>
-      </c>
-      <c r="K8" t="str" s="6">
+      <c r="J8" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" ht="66" customHeight="1" spans="1:11">
+      <c r="B9" s="6">
+        <v>3</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="H9" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" ht="66.0" customHeight="1">
-      <c r="B9" t="n" s="6">
-        <v>3</v>
-      </c>
-      <c r="C9" t="str" s="7">
-        <v>临时小兵攻击</v>
-      </c>
-      <c r="D9" t="str" s="6">
-        <v>战争</v>
-      </c>
-      <c r="E9" t="str" s="7">
-        <v>$Lang$临时小兵攻击</v>
-      </c>
-      <c r="F9" t="str" s="7">
-        <v>科技图标_临时小兵攻击</v>
-      </c>
-      <c r="G9" t="str" s="7">
-        <v>$Lang$临时小兵攻击_说明</v>
-      </c>
-      <c r="H9" t="n" s="6">
-        <v>1</v>
-      </c>
-      <c r="I9" t="n" s="6">
+      <c r="I9" s="6">
         <v>1</v>
       </c>
     </row>
@@ -1706,17 +1868,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:I15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelRow="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="13.3333333333333" style="2" customWidth="1"/>
     <col min="2" max="2" width="9.77777777777778" style="2" customWidth="1"/>
-    <col min="3" max="3" width="6.66666666666667" style="2" customWidth="1"/>
+    <col min="3" max="3" width="15.2222222222222" style="2" customWidth="1"/>
     <col min="4" max="4" width="17.8888888888889" style="2" customWidth="1"/>
     <col min="5" max="5" width="7.88888888888889" style="2" customWidth="1"/>
     <col min="6" max="6" width="12.1111111111111" style="2" customWidth="1"/>
     <col min="7" max="7" width="14.3333333333333" style="2" customWidth="1"/>
     <col min="8" max="8" width="12.8888888888889" style="2" customWidth="1"/>
-    <col min="9" max="9" width="7.88888888888889" style="2" customWidth="1"/>
+    <col min="9" max="9" width="26.4444444444444" style="2" customWidth="1"/>
     <col min="10" max="16384" width="9" style="2" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1744,36 +1906,36 @@
     </row>
     <row r="3" s="1" customFormat="1" spans="1:9">
       <c r="A3" s="4" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>2</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:9">
       <c r="A4" s="5" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>12</v>
@@ -1782,19 +1944,19 @@
         <v>13</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>18</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="I4" s="5" t="s">
         <v>17</v>
@@ -1846,10 +2008,10 @@
         <v>32</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>32</v>
@@ -1858,238 +2020,238 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" ht="82.5" customHeight="1">
-      <c r="B7" t="n" s="6">
+    <row r="7" spans="1:9">
+      <c r="B7" s="6">
         <v>1001</v>
       </c>
-      <c r="C7" t="str" s="7">
-        <v>临时金币产出_1级</v>
-      </c>
-      <c r="D7" t="str" s="6">
-        <v>临时金币产出</v>
-      </c>
-      <c r="E7" t="n" s="6">
+      <c r="C7" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="6">
         <v>1</v>
       </c>
-      <c r="F7" t="str" s="7">
-        <v>金币//木材</v>
-      </c>
-      <c r="G7" t="str" s="6">
-        <v>100//50</v>
-      </c>
-      <c r="H7" t="n" s="6">
+      <c r="F7" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="H7" s="6">
         <v>60</v>
       </c>
-      <c r="I7" t="str" s="7">
-        <v>$Lang$临时金币产出_1级_说明</v>
-      </c>
-    </row>
-    <row r="8" ht="82.5" customHeight="1">
-      <c r="B8" t="n" s="6">
+      <c r="I7" s="6" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="B8" s="6">
         <v>1002</v>
       </c>
-      <c r="C8" t="str" s="7">
-        <v>临时金币产出_2级</v>
-      </c>
-      <c r="D8" t="str" s="6">
-        <v>临时金币产出</v>
-      </c>
-      <c r="E8" t="n" s="6">
+      <c r="C8" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="6">
         <v>2</v>
       </c>
-      <c r="F8" t="str" s="7">
-        <v>金币//木材</v>
-      </c>
-      <c r="G8" t="str" s="6">
-        <v>200//100</v>
-      </c>
-      <c r="H8" t="n" s="6">
+      <c r="F8" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="H8" s="6">
         <v>120</v>
       </c>
-      <c r="I8" t="str" s="7">
-        <v>$Lang$临时金币产出_2级_说明</v>
-      </c>
-    </row>
-    <row r="9" ht="82.5" customHeight="1">
-      <c r="B9" t="n" s="6">
+      <c r="I8" s="6" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="B9" s="6">
         <v>1003</v>
       </c>
-      <c r="C9" t="str" s="7">
-        <v>临时金币产出_3级</v>
-      </c>
-      <c r="D9" t="str" s="6">
-        <v>临时金币产出</v>
-      </c>
-      <c r="E9" t="n" s="6">
+      <c r="C9" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="6">
         <v>3</v>
       </c>
-      <c r="F9" t="str" s="7">
-        <v>金币//木材</v>
-      </c>
-      <c r="G9" t="str" s="6">
-        <v>300//150</v>
-      </c>
-      <c r="H9" t="n" s="6">
+      <c r="F9" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H9" s="6">
         <v>180</v>
       </c>
-      <c r="I9" t="str" s="7">
-        <v>$Lang$临时金币产出_3级_说明</v>
-      </c>
-    </row>
-    <row r="10" ht="82.5" customHeight="1">
-      <c r="B10" t="n" s="6">
+      <c r="I9" s="6" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="B10" s="6">
         <v>2001</v>
       </c>
-      <c r="C10" t="str" s="7">
-        <v>临时木材产出_1级</v>
-      </c>
-      <c r="D10" t="str" s="6">
-        <v>临时木材产出</v>
-      </c>
-      <c r="E10" t="n" s="6">
+      <c r="C10" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10" s="6">
         <v>1</v>
       </c>
-      <c r="F10" t="str" s="7">
-        <v>金币//木材</v>
-      </c>
-      <c r="G10" t="str" s="6">
-        <v>100//50</v>
-      </c>
-      <c r="H10" t="n" s="6">
+      <c r="F10" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="H10" s="6">
         <v>60</v>
       </c>
-      <c r="I10" t="str" s="7">
-        <v>$Lang$临时木材产出_1级_说明</v>
-      </c>
-    </row>
-    <row r="11" ht="82.5" customHeight="1">
-      <c r="B11" t="n" s="6">
+      <c r="I10" s="6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="B11" s="6">
         <v>2002</v>
       </c>
-      <c r="C11" t="str" s="7">
-        <v>临时木材产出_2级</v>
-      </c>
-      <c r="D11" t="str" s="6">
-        <v>临时木材产出</v>
-      </c>
-      <c r="E11" t="n" s="6">
+      <c r="C11" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E11" s="6">
         <v>2</v>
       </c>
-      <c r="F11" t="str" s="7">
-        <v>金币//木材</v>
-      </c>
-      <c r="G11" t="str" s="6">
-        <v>200//100</v>
-      </c>
-      <c r="H11" t="n" s="6">
+      <c r="F11" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="H11" s="6">
         <v>120</v>
       </c>
-      <c r="I11" t="str" s="7">
-        <v>$Lang$临时木材产出_2级_说明</v>
-      </c>
-    </row>
-    <row r="12" ht="82.5" customHeight="1">
-      <c r="B12" t="n" s="6">
+      <c r="I11" s="6" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="B12" s="6">
         <v>2003</v>
       </c>
-      <c r="C12" t="str" s="7">
-        <v>临时木材产出_3级</v>
-      </c>
-      <c r="D12" t="str" s="6">
-        <v>临时木材产出</v>
-      </c>
-      <c r="E12" t="n" s="6">
+      <c r="C12" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E12" s="6">
         <v>3</v>
       </c>
-      <c r="F12" t="str" s="7">
-        <v>金币//木材</v>
-      </c>
-      <c r="G12" t="str" s="6">
-        <v>300//150</v>
-      </c>
-      <c r="H12" t="n" s="6">
+      <c r="F12" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H12" s="6">
         <v>180</v>
       </c>
-      <c r="I12" t="str" s="7">
-        <v>$Lang$临时木材产出_3级_说明</v>
-      </c>
-    </row>
-    <row r="13" ht="82.5" customHeight="1">
-      <c r="B13" t="n" s="6">
+      <c r="I12" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="B13" s="6">
         <v>3001</v>
       </c>
-      <c r="C13" t="str" s="7">
-        <v>临时小兵攻击_1级</v>
-      </c>
-      <c r="D13" t="str" s="6">
-        <v>临时小兵攻击</v>
-      </c>
-      <c r="E13" t="n" s="6">
+      <c r="C13" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="E13" s="6">
         <v>1</v>
       </c>
-      <c r="F13" t="str" s="7">
-        <v>金币//木材</v>
-      </c>
-      <c r="G13" t="str" s="6">
-        <v>100//50</v>
-      </c>
-      <c r="H13" t="n" s="6">
+      <c r="F13" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="H13" s="6">
         <v>60</v>
       </c>
-      <c r="I13" t="str" s="7">
-        <v>$Lang$临时小兵攻击_1级_说明</v>
-      </c>
-    </row>
-    <row r="14" ht="82.5" customHeight="1">
-      <c r="B14" t="n" s="6">
+      <c r="I13" s="6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="B14" s="6">
         <v>3002</v>
       </c>
-      <c r="C14" t="str" s="7">
-        <v>临时小兵攻击_2级</v>
-      </c>
-      <c r="D14" t="str" s="6">
-        <v>临时小兵攻击</v>
-      </c>
-      <c r="E14" t="n" s="6">
+      <c r="C14" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="E14" s="6">
         <v>2</v>
       </c>
-      <c r="F14" t="str" s="7">
-        <v>金币//木材</v>
-      </c>
-      <c r="G14" t="str" s="6">
-        <v>200//100</v>
-      </c>
-      <c r="H14" t="n" s="6">
+      <c r="F14" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="H14" s="6">
         <v>120</v>
       </c>
-      <c r="I14" t="str" s="7">
-        <v>$Lang$临时小兵攻击_2级_说明</v>
-      </c>
-    </row>
-    <row r="15" ht="82.5" customHeight="1">
-      <c r="B15" t="n" s="6">
+      <c r="I14" s="6" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="B15" s="6">
         <v>3003</v>
       </c>
-      <c r="C15" t="str" s="7">
-        <v>临时小兵攻击_3级</v>
-      </c>
-      <c r="D15" t="str" s="6">
-        <v>临时小兵攻击</v>
-      </c>
-      <c r="E15" t="n" s="6">
+      <c r="C15" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="E15" s="6">
         <v>3</v>
       </c>
-      <c r="F15" t="str" s="7">
-        <v>金币//木材</v>
-      </c>
-      <c r="G15" t="str" s="6">
-        <v>300//150</v>
-      </c>
-      <c r="H15" t="n" s="6">
+      <c r="F15" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H15" s="6">
         <v>180</v>
       </c>
-      <c r="I15" t="str" s="7">
-        <v>$Lang$临时小兵攻击_3级_说明</v>
+      <c r="I15" s="6" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -2102,13 +2264,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelRow="5" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelRow="7" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="13.1111111111111" style="2" customWidth="1"/>
     <col min="2" max="2" width="9.77777777777778" style="2" customWidth="1"/>
     <col min="3" max="3" width="6.66666666666667" style="2" customWidth="1"/>
-    <col min="4" max="4" width="7.88888888888889" style="2" customWidth="1"/>
-    <col min="5" max="5" width="11.8888888888889" style="2" customWidth="1"/>
+    <col min="4" max="4" width="19" style="2" customWidth="1"/>
+    <col min="5" max="5" width="12.2222222222222" style="2" customWidth="1"/>
     <col min="6" max="6" width="15.3333333333333" style="2" customWidth="1"/>
     <col min="7" max="7" width="7.88888888888889" style="2" customWidth="1"/>
     <col min="8" max="16384" width="9" style="2" customWidth="1"/>
@@ -2134,30 +2296,30 @@
     </row>
     <row r="3" s="1" customFormat="1" spans="1:7">
       <c r="A3" s="4" t="s">
-        <v>51</v>
+        <v>88</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>52</v>
+        <v>89</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>2</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>54</v>
+        <v>91</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>55</v>
+        <v>92</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:7">
       <c r="A4" s="5" t="s">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>12</v>
@@ -2172,7 +2334,7 @@
         <v>16</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>17</v>
@@ -2224,37 +2386,37 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" ht="66.0" customHeight="1">
-      <c r="B7" t="n" s="6">
+    <row r="7" spans="1:7">
+      <c r="B7" s="6">
         <v>1</v>
       </c>
-      <c r="C7" t="str" s="6">
-        <v>内政</v>
-      </c>
-      <c r="D7" t="str" s="7">
-        <v>$Lang$科技分类_内政</v>
-      </c>
-      <c r="E7" t="str" s="7">
-        <v>科技图标_内政</v>
-      </c>
-      <c r="F7" t="n" s="6">
+      <c r="C7" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="F7" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="8" ht="66.0" customHeight="1">
-      <c r="B8" t="n" s="6">
+    <row r="8" spans="1:7">
+      <c r="B8" s="6">
         <v>2</v>
       </c>
-      <c r="C8" t="str" s="6">
-        <v>战争</v>
-      </c>
-      <c r="D8" t="str" s="7">
-        <v>$Lang$科技分类_战争</v>
-      </c>
-      <c r="E8" t="str" s="7">
-        <v>科技图标_战争</v>
-      </c>
-      <c r="F8" t="n" s="6">
+      <c r="C8" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="F8" s="6">
         <v>1</v>
       </c>
     </row>
@@ -2268,11 +2430,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelRow="5" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="13.7777777777778" style="2" customWidth="1"/>
     <col min="2" max="2" width="6.44444444444444" style="2" customWidth="1"/>
-    <col min="3" max="3" width="6.66666666666667" style="2" customWidth="1"/>
+    <col min="3" max="3" width="19.6666666666667" style="2" customWidth="1"/>
     <col min="4" max="4" width="17" style="2" customWidth="1"/>
     <col min="5" max="5" width="17.3333333333333" style="2" customWidth="1"/>
     <col min="6" max="6" width="16.1111111111111" style="2" customWidth="1"/>
@@ -2300,30 +2462,30 @@
     </row>
     <row r="3" s="1" customFormat="1" spans="1:7">
       <c r="A3" s="4" t="s">
-        <v>59</v>
+        <v>100</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>60</v>
+        <v>101</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>2</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>61</v>
+        <v>102</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>62</v>
+        <v>103</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>63</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:7">
       <c r="A4" s="5" t="s">
-        <v>64</v>
+        <v>105</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>12</v>
@@ -2332,16 +2494,16 @@
         <v>13</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>65</v>
+        <v>106</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>66</v>
+        <v>107</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>67</v>
+        <v>108</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>68</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:7">
@@ -2364,7 +2526,7 @@
         <v>24</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>69</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:7">
@@ -2378,75 +2540,75 @@
         <v>30</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>70</v>
+        <v>111</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>71</v>
+        <v>112</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>72</v>
+        <v>113</v>
       </c>
       <c r="G6" s="5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="7" ht="82.5" customHeight="1">
-      <c r="B7" t="n" s="6">
+    <row r="7" spans="1:7">
+      <c r="B7" s="6">
         <v>3001</v>
       </c>
-      <c r="C7" t="str" s="7">
-        <v>临时小兵攻击_1级_效果</v>
-      </c>
-      <c r="D7" t="str" s="7">
-        <v>临时小兵攻击_1级</v>
-      </c>
-      <c r="E7" t="str" s="6">
-        <v>小兵</v>
-      </c>
-      <c r="F7" t="str" s="6">
-        <v>攻击</v>
-      </c>
-      <c r="G7" t="n" s="6">
+      <c r="C7" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="G7" s="6">
         <v>0.01</v>
       </c>
     </row>
-    <row r="8" ht="82.5" customHeight="1">
-      <c r="B8" t="n" s="6">
+    <row r="8" spans="1:7">
+      <c r="B8" s="6">
         <v>3002</v>
       </c>
-      <c r="C8" t="str" s="7">
-        <v>临时小兵攻击_2级_效果</v>
-      </c>
-      <c r="D8" t="str" s="7">
-        <v>临时小兵攻击_2级</v>
-      </c>
-      <c r="E8" t="str" s="6">
-        <v>小兵</v>
-      </c>
-      <c r="F8" t="str" s="6">
-        <v>攻击</v>
-      </c>
-      <c r="G8" t="n" s="6">
+      <c r="C8" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="G8" s="6">
         <v>0.02</v>
       </c>
     </row>
-    <row r="9" ht="82.5" customHeight="1">
-      <c r="B9" t="n" s="6">
+    <row r="9" spans="1:7">
+      <c r="B9" s="6">
         <v>3003</v>
       </c>
-      <c r="C9" t="str" s="7">
-        <v>临时小兵攻击_3级_效果</v>
-      </c>
-      <c r="D9" t="str" s="7">
-        <v>临时小兵攻击_3级</v>
-      </c>
-      <c r="E9" t="str" s="6">
-        <v>小兵</v>
-      </c>
-      <c r="F9" t="str" s="6">
-        <v>攻击</v>
-      </c>
-      <c r="G9" t="n" s="6">
+      <c r="C9" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="G9" s="6">
         <v>0.03</v>
       </c>
     </row>
@@ -2460,11 +2622,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelRow="5" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="16.8888888888889" style="2" customWidth="1"/>
     <col min="2" max="2" width="6.44444444444444" style="2" customWidth="1"/>
-    <col min="3" max="3" width="6.66666666666667" style="2" customWidth="1"/>
+    <col min="3" max="3" width="19.6666666666667" style="2" customWidth="1"/>
     <col min="4" max="4" width="17" style="2" customWidth="1"/>
     <col min="5" max="5" width="12.4444444444444" style="2" customWidth="1"/>
     <col min="6" max="6" width="17.2222222222222" style="2" customWidth="1"/>
@@ -2489,27 +2651,27 @@
     </row>
     <row r="3" s="1" customFormat="1" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>73</v>
+        <v>119</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>60</v>
+        <v>101</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>2</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>74</v>
+        <v>120</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>75</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:6">
       <c r="A4" s="5" t="s">
-        <v>76</v>
+        <v>122</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>12</v>
@@ -2518,13 +2680,13 @@
         <v>13</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>65</v>
+        <v>106</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>77</v>
+        <v>123</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>78</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:6">
@@ -2544,7 +2706,7 @@
         <v>24</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>69</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:6">
@@ -2558,114 +2720,114 @@
         <v>30</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>70</v>
+        <v>111</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="7" ht="82.5" customHeight="1">
-      <c r="B7" t="n" s="6">
+    <row r="7" spans="1:6">
+      <c r="B7" s="6">
         <v>1001</v>
       </c>
-      <c r="C7" t="str" s="7">
-        <v>临时金币产出_1级_效果</v>
-      </c>
-      <c r="D7" t="str" s="7">
-        <v>临时金币产出_1级</v>
-      </c>
-      <c r="E7" t="str" s="6">
-        <v>金币</v>
-      </c>
-      <c r="F7" t="n" s="6">
+      <c r="C7" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="F7" s="6">
         <v>0.01</v>
       </c>
     </row>
-    <row r="8" ht="82.5" customHeight="1">
-      <c r="B8" t="n" s="6">
+    <row r="8" spans="1:6">
+      <c r="B8" s="6">
         <v>1002</v>
       </c>
-      <c r="C8" t="str" s="7">
-        <v>临时金币产出_2级_效果</v>
-      </c>
-      <c r="D8" t="str" s="7">
-        <v>临时金币产出_2级</v>
-      </c>
-      <c r="E8" t="str" s="6">
-        <v>金币</v>
-      </c>
-      <c r="F8" t="n" s="6">
+      <c r="C8" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="F8" s="6">
         <v>0.02</v>
       </c>
     </row>
-    <row r="9" ht="82.5" customHeight="1">
-      <c r="B9" t="n" s="6">
+    <row r="9" spans="1:6">
+      <c r="B9" s="6">
         <v>1003</v>
       </c>
-      <c r="C9" t="str" s="7">
-        <v>临时金币产出_3级_效果</v>
-      </c>
-      <c r="D9" t="str" s="7">
-        <v>临时金币产出_3级</v>
-      </c>
-      <c r="E9" t="str" s="6">
-        <v>金币</v>
-      </c>
-      <c r="F9" t="n" s="6">
+      <c r="C9" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="F9" s="6">
         <v>0.03</v>
       </c>
     </row>
-    <row r="10" ht="82.5" customHeight="1">
-      <c r="B10" t="n" s="6">
+    <row r="10" spans="1:6">
+      <c r="B10" s="6">
         <v>2001</v>
       </c>
-      <c r="C10" t="str" s="7">
-        <v>临时木材产出_1级_效果</v>
-      </c>
-      <c r="D10" t="str" s="7">
-        <v>临时木材产出_1级</v>
-      </c>
-      <c r="E10" t="str" s="6">
-        <v>木材</v>
-      </c>
-      <c r="F10" t="n" s="6">
+      <c r="C10" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="F10" s="6">
         <v>0.01</v>
       </c>
     </row>
-    <row r="11" ht="82.5" customHeight="1">
-      <c r="B11" t="n" s="6">
+    <row r="11" spans="1:6">
+      <c r="B11" s="6">
         <v>2002</v>
       </c>
-      <c r="C11" t="str" s="7">
-        <v>临时木材产出_2级_效果</v>
-      </c>
-      <c r="D11" t="str" s="7">
-        <v>临时木材产出_2级</v>
-      </c>
-      <c r="E11" t="str" s="6">
-        <v>木材</v>
-      </c>
-      <c r="F11" t="n" s="6">
+      <c r="C11" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="F11" s="6">
         <v>0.02</v>
       </c>
     </row>
-    <row r="12" ht="82.5" customHeight="1">
-      <c r="B12" t="n" s="6">
+    <row r="12" spans="1:6">
+      <c r="B12" s="6">
         <v>2003</v>
       </c>
-      <c r="C12" t="str" s="7">
-        <v>临时木材产出_3级_效果</v>
-      </c>
-      <c r="D12" t="str" s="7">
-        <v>临时木材产出_3级</v>
-      </c>
-      <c r="E12" t="str" s="6">
-        <v>木材</v>
-      </c>
-      <c r="F12" t="n" s="6">
+      <c r="C12" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="F12" s="6">
         <v>0.03</v>
       </c>
     </row>
